--- a/NECP Scenario/Results/Regional Results/EL63_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL63_Capacity.xlsx
@@ -507,25 +507,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.176539602227794E-11</v>
+        <v>1.737116463908899E-11</v>
       </c>
       <c r="C2">
-        <v>6.160909903819702E-12</v>
+        <v>9.096365337689696E-12</v>
       </c>
       <c r="D2">
-        <v>9.052354854027144E-12</v>
+        <v>1.336547267947458E-11</v>
       </c>
       <c r="E2">
-        <v>1.330098311619531E-11</v>
+        <v>1.963840118706332E-11</v>
       </c>
       <c r="F2">
-        <v>1.954358152904776E-11</v>
+        <v>2.88553432444599E-11</v>
       </c>
       <c r="G2">
-        <v>2.871587141023811E-11</v>
+        <v>4.239787100552689E-11</v>
       </c>
       <c r="H2">
-        <v>1.740400336508676E-10</v>
+        <v>2.569636220023244E-10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.524675053040334E-08</v>
+        <v>3.744802681757359E-08</v>
       </c>
       <c r="C3">
-        <v>2.532996792662813E-08</v>
+        <v>3.757758503269906E-08</v>
       </c>
       <c r="D3">
-        <v>5.634301036384715E-08</v>
+        <v>8.340246983589175E-08</v>
       </c>
       <c r="E3">
-        <v>1.208346075527913E-07</v>
+        <v>1.611004001617617E-07</v>
       </c>
       <c r="F3">
-        <v>4.038266373905545E-07</v>
+        <v>4.715463404016302E-07</v>
       </c>
       <c r="G3">
-        <v>2.740029301476744E-06</v>
+        <v>9.423831096913037E-06</v>
       </c>
       <c r="H3">
-        <v>0.1972078980063146</v>
+        <v>0.2940359976011858</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -562,22 +562,22 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.0503056543025595</v>
+        <v>0.0500937776191056</v>
       </c>
       <c r="D4">
-        <v>0.050305654316616</v>
+        <v>0.0500937776413563</v>
       </c>
       <c r="E4">
-        <v>0.0503056543625449</v>
+        <v>0.0500937777057821</v>
       </c>
       <c r="F4">
-        <v>0.0503056544009061</v>
+        <v>0.0500937778050743</v>
       </c>
       <c r="G4">
-        <v>0.0503056544558772</v>
+        <v>0.0500937779296524</v>
       </c>
       <c r="H4">
-        <v>0.0503056546671503</v>
+        <v>0.0500937783486595</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -692,22 +692,22 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>2.022299824207125E-08</v>
+        <v>2.957170067505404E-08</v>
       </c>
       <c r="D9">
-        <v>2.309224013031672E-08</v>
+        <v>3.507564280313714E-08</v>
       </c>
       <c r="E9">
-        <v>2.398645760070268E-08</v>
+        <v>3.585980888282283E-08</v>
       </c>
       <c r="F9">
-        <v>2.401356247286613E-08</v>
+        <v>3.589916006152955E-08</v>
       </c>
       <c r="G9">
-        <v>2.405796332523766E-08</v>
+        <v>3.596126109755478E-08</v>
       </c>
       <c r="H9">
-        <v>1.214341779439765E-07</v>
+        <v>1.844971219919472E-07</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.341119932004587</v>
+        <v>1.341119932005093</v>
       </c>
       <c r="C13">
-        <v>1.341119932006312</v>
+        <v>1.341119932007637</v>
       </c>
       <c r="D13">
-        <v>1.341119932010649</v>
+        <v>1.341119932011731</v>
       </c>
       <c r="E13">
-        <v>1.341119932018866</v>
+        <v>1.341119932022933</v>
       </c>
       <c r="F13">
-        <v>1.341119932032371</v>
+        <v>1.34111993203996</v>
       </c>
       <c r="G13">
-        <v>1.341119932058675</v>
+        <v>1.341119932074798</v>
       </c>
       <c r="H13">
-        <v>1.34111993234664</v>
+        <v>1.341119932406186</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -923,25 +923,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1.809244279703224E-08</v>
+        <v>2.677011412402673E-08</v>
       </c>
       <c r="C18">
-        <v>1.810372927873688E-08</v>
+        <v>2.678712280516868E-08</v>
       </c>
       <c r="D18">
-        <v>3.435974039162495E-08</v>
+        <v>5.152373668762569E-08</v>
       </c>
       <c r="E18">
-        <v>7.728287662331429E-08</v>
+        <v>1.098686517370012E-07</v>
       </c>
       <c r="F18">
-        <v>2.236775148099213E-07</v>
+        <v>2.910705050900077E-07</v>
       </c>
       <c r="G18">
-        <v>4.020626646460022E-07</v>
+        <v>6.696638304849292E-07</v>
       </c>
       <c r="H18">
-        <v>2.362373743986921E-06</v>
+        <v>4.425619498279212E-06</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -952,22 +952,22 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>1.043730664358844E-08</v>
+        <v>1.559702667368689E-08</v>
       </c>
       <c r="D19">
-        <v>1.51455442820894E-08</v>
+        <v>2.321427788602511E-08</v>
       </c>
       <c r="E19">
-        <v>3.605078464572434E-08</v>
+        <v>5.371642616700491E-08</v>
       </c>
       <c r="F19">
-        <v>1.420359016991717E-07</v>
+        <v>1.882164940011083E-07</v>
       </c>
       <c r="G19">
-        <v>1.052958404560531E-06</v>
+        <v>2.02394948608495E-06</v>
       </c>
       <c r="H19">
-        <v>0.5531214935898632</v>
+        <v>0.5531214940914952</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1027,25 +1027,25 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.911293851662961E-08</v>
+        <v>4.304522052535896E-08</v>
       </c>
       <c r="C22">
-        <v>2.912988753093947E-08</v>
+        <v>4.307028981634349E-08</v>
       </c>
       <c r="D22">
-        <v>2.9285474437844E-08</v>
+        <v>4.33031314310524E-08</v>
       </c>
       <c r="E22">
-        <v>4.021012513138812E-08</v>
+        <v>5.956373818360585E-08</v>
       </c>
       <c r="F22">
-        <v>5.723310590788324E-08</v>
+        <v>8.490298346903035E-08</v>
       </c>
       <c r="G22">
-        <v>8.248688163335304E-08</v>
+        <v>1.218981124741474E-07</v>
       </c>
       <c r="H22">
-        <v>5.072703633700058E-07</v>
+        <v>7.55600274554548E-07</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>5.836047262479628E-09</v>
+        <v>8.59632772443378E-09</v>
       </c>
       <c r="D24">
-        <v>2.239417112884939E-08</v>
+        <v>3.290857244410736E-08</v>
       </c>
       <c r="E24">
-        <v>7.366477268385525E-08</v>
+        <v>1.175396951615844E-07</v>
       </c>
       <c r="F24">
-        <v>3.014270589768903E-07</v>
+        <v>8.041335488412171E-07</v>
       </c>
       <c r="G24">
-        <v>0.0350279119589211</v>
+        <v>0.0496672331807171</v>
       </c>
       <c r="H24">
-        <v>0.3647510591619101</v>
+        <v>0.5576296686835348</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1160,22 +1160,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.2873421220938762</v>
+        <v>0.2654178796420257</v>
       </c>
       <c r="D27">
-        <v>0.4365491317033532</v>
+        <v>0.525026207331615</v>
       </c>
       <c r="E27">
-        <v>1.057323447458512</v>
+        <v>0.9464464463051814</v>
       </c>
       <c r="F27">
-        <v>1.219511101312921</v>
+        <v>1.069509584142408</v>
       </c>
       <c r="G27">
-        <v>1.479506861160144</v>
+        <v>1.28159563399823</v>
       </c>
       <c r="H27">
-        <v>2.453422193924983</v>
+        <v>2.453422192330007</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1212,22 +1212,22 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>8.241937703453024E-09</v>
+        <v>1.225364735165103E-08</v>
       </c>
       <c r="D29">
-        <v>2.601686095165868E-08</v>
+        <v>4.052562341198199E-08</v>
       </c>
       <c r="E29">
-        <v>7.202996635758946E-08</v>
+        <v>1.223245297063583E-07</v>
       </c>
       <c r="F29">
-        <v>3.742342076044464E-07</v>
+        <v>1.400628023501622E-06</v>
       </c>
       <c r="G29">
-        <v>0.7240468633843116</v>
+        <v>0.7240468629629621</v>
       </c>
       <c r="H29">
-        <v>0.7240468644451175</v>
+        <v>0.7240468643569012</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1264,22 +1264,22 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>5.097603179925491E-09</v>
+        <v>7.559925088616607E-09</v>
       </c>
       <c r="D31">
-        <v>6.935619311890741E-09</v>
+        <v>1.037844891335903E-08</v>
       </c>
       <c r="E31">
-        <v>1.142805090061592E-08</v>
+        <v>1.718682374230213E-08</v>
       </c>
       <c r="F31">
-        <v>1.807336598132321E-08</v>
+        <v>2.719435403499618E-08</v>
       </c>
       <c r="G31">
-        <v>2.626070517832174E-08</v>
+        <v>3.888001831497704E-08</v>
       </c>
       <c r="H31">
-        <v>1.557548407627236E-07</v>
+        <v>2.393428333415553E-07</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1316,22 +1316,22 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0.1865889757309496</v>
+        <v>0.091406555247365</v>
       </c>
       <c r="D33">
-        <v>0.1865889757938738</v>
+        <v>0.0914065553426964</v>
       </c>
       <c r="E33">
-        <v>0.1865889760000876</v>
+        <v>0.0914065562612759</v>
       </c>
       <c r="F33">
-        <v>0.1865889761349598</v>
+        <v>0.0914065564908785</v>
       </c>
       <c r="G33">
-        <v>0.1865889762798732</v>
+        <v>0.0914065566755735</v>
       </c>
       <c r="H33">
-        <v>0.1865889772140219</v>
+        <v>0.0914065578479672</v>
       </c>
     </row>
     <row r="34" spans="1:8">
